--- a/GourmetProject/GameConfig/Datas/dish_base.xlsx
+++ b/GourmetProject/GameConfig/Datas/dish_base.xlsx
@@ -491,7 +491,6 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
           <t>rice</t>
@@ -522,7 +521,6 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
           <t>egg</t>
@@ -553,7 +551,6 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>soup</t>
@@ -584,7 +581,6 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
           <t>fish</t>
@@ -615,7 +611,6 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
           <t>noodle</t>
@@ -641,25 +636,18 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>X.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="G8" t="inlineStr">
+        <is>
           <t>XX</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>X.</t>
-        </is>
-      </c>
-    </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
           <t>dumpling</t>
@@ -690,12 +678,6 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>.X</t>
@@ -703,7 +685,6 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
           <t>chili</t>
@@ -734,7 +715,6 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
           <t>orange</t>
@@ -765,12 +745,6 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>XX</t>
@@ -778,7 +752,6 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
           <t>cake</t>
@@ -809,12 +782,6 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>.X.</t>
@@ -822,7 +789,6 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
           <t>feast</t>

--- a/GourmetProject/GameConfig/Datas/dish_base.xlsx
+++ b/GourmetProject/GameConfig/Datas/dish_base.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,117 +456,124 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>##comment</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>菜品基础ID</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>菜品名称</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>基础美味度</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>图标资源路径</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>是否允许旋转摆放</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>菜品形状行列表</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>##type</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>list,string</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>rice</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>米饭</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Sprites/Dishes/rice</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>X</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>egg</t>
+          <t>rice</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>煎蛋</t>
+          <t>米饭</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sprites/Dishes/egg</t>
+          <t>Sprites/Dishes/rice</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>XX</t>
+          <t>X</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>soup</t>
+          <t>egg</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>鲜汤</t>
+          <t>煎蛋</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sprites/Dishes/soup</t>
+          <t>Sprites/Dishes/egg</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -583,20 +590,20 @@
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>soup</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>清蒸鱼</t>
+          <t>鲜汤</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sprites/Dishes/fish</t>
+          <t>Sprites/Dishes/soup</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -606,213 +613,243 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>XXX</t>
+          <t>XX</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
+          <t>fish</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>清蒸鱼</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>15</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sprites/Dishes/fish</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>XXX</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
           <t>noodle</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>拌面</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D8" t="n">
         <v>12</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Sprites/Dishes/noodle</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>X.</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="G8" t="inlineStr">
+    <row r="9">
+      <c r="G9" t="inlineStr">
         <is>
           <t>XX</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" t="inlineStr">
+    <row r="10">
+      <c r="B10" t="inlineStr">
         <is>
           <t>dumpling</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>饺子</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D10" t="n">
         <v>11</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Sprites/Dishes/dumpling</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>XX</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="G10" t="inlineStr">
+    <row r="11">
+      <c r="G11" t="inlineStr">
         <is>
           <t>.X</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>chili</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>辣椒</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>4</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Sprites/Dishes/chili</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>X</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
+          <t>chili</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>辣椒</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sprites/Dishes/chili</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
           <t>orange</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>橙子</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D13" t="n">
         <v>10</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Sprites/Dishes/orange</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>XX</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="G13" t="inlineStr">
+    <row r="14">
+      <c r="G14" t="inlineStr">
         <is>
           <t>XX</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" t="inlineStr">
+    <row r="15">
+      <c r="B15" t="inlineStr">
         <is>
           <t>cake</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>蛋糕</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D15" t="n">
         <v>20</v>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Sprites/Dishes/cake</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>XXX</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="G15" t="inlineStr">
+    <row r="16">
+      <c r="G16" t="inlineStr">
         <is>
           <t>.X.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" t="inlineStr">
+    <row r="17">
+      <c r="B17" t="inlineStr">
         <is>
           <t>feast</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>满汉全席</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D17" t="n">
         <v>25</v>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Sprites/Dishes/feast</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>XXXX</t>
         </is>
